--- a/materials/chatgpt-web-basics/02_파일_맡기고_결과파일_받기/강사용/정답_대조표.xlsx
+++ b/materials/chatgpt-web-basics/02_파일_맡기고_결과파일_받기/강사용/정답_대조표.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>"정리"의 뜻은 내가 정한다</t>
+          <t>규칙을 정해 주고 CSV 정리 맡기기</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>열 이름이 달라도 하나로</t>
+          <t>열 이름이 다른 파일 5개 하나로 합치기</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>열 이름이 달라도 하나로</t>
+          <t>열 이름이 다른 파일 5개 하나로 합치기</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>짚어서 한 번 더</t>
+          <t>틀린 곳 짚어서 다시 맡기기</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>짚어서 한 번 더</t>
+          <t>틀린 곳 짚어서 다시 맡기기</t>
         </is>
       </c>
     </row>
